--- a/reports/module-data-integration-audit/2026-07-27/METRIC_DEFINITION_DUPLICATION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/METRIC_DEFINITION_DUPLICATION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Duplication" sheetId="1" r:id="R76b319ffc3f14dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Duplication" sheetId="1" r:id="Rd36ae6c6f76a4f30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -342,19 +342,19 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>Moves</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>public.measured</x:v>
+        <x:v>public.source_contract_evidence_metrics</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
+        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
       </x:c>
       <x:c r="E2" s="5" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="F2" s="5" t="str">
         <x:v>shared metric definition registry; domain observations remain local until published</x:v>
@@ -365,16 +365,16 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>Value / outcome</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>public.cost</x:v>
+        <x:v>public.source_meeting_outcomes</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
+        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
         <x:v>Medium</x:v>
@@ -394,7 +394,7 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>public.outcome</x:v>
+        <x:v>public.source_value_chain</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
@@ -417,7 +417,7 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>public.PHASE_C_VALUE_MODES</x:v>
+        <x:v>public.source_value_levers</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
@@ -434,19 +434,19 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>Value / outcome</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>public.SLA</x:v>
+        <x:v>public.source_value_lines</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
+        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
         <x:v>shared metric definition registry; domain observations remain local until published</x:v>
@@ -457,13 +457,13 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>Value / outcome</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>public.source_contract_evidence_metrics</x:v>
+        <x:v>public.source_value_states</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
@@ -483,13 +483,13 @@
         <x:v>Value / outcome</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>public.source_meeting_outcomes</x:v>
+        <x:v>cio_tower.mart_value_funnel</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+        <x:v>Derived read model or reporting projection.</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
         <x:v>Medium</x:v>
@@ -503,16 +503,16 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>public.source_value_chain</x:v>
+        <x:v>cio_tower.measure_results</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+        <x:v>Persisted module object requiring owner review.</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
         <x:v>Medium</x:v>
@@ -526,16 +526,16 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>knowledge.metric_definition</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>public.source_value_levers</x:v>
+        <x:v>cio_tower.measures</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+        <x:v>Persisted module object requiring owner review.</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
         <x:v>Medium</x:v>
@@ -552,10 +552,10 @@
         <x:v>Value / outcome</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>public.source_value_lines</x:v>
+        <x:v>public.ai_control_agent_outcomes</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
         <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
@@ -572,13 +572,13 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>Operational performance</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="C12" s="5" t="str">
-        <x:v>public.source_value_states</x:v>
+        <x:v>public.ai_control_dora_metrics</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
         <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
@@ -595,16 +595,16 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>public.value</x:v>
+        <x:v>public.ai_control_spend_contracts</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+        <x:v>Risk/control governance or monitoring substrate.</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
         <x:v>Medium</x:v>
@@ -618,19 +618,19 @@
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>to_be_mapped</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>public.value_source</x:v>
+        <x:v>public.dora_baselines</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+        <x:v>Persisted module object requiring owner review.</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>Medium</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
         <x:v>shared metric definition registry; domain observations remain local until published</x:v>
@@ -641,16 +641,16 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>to_be_mapped</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>public.valueType</x:v>
+        <x:v>public.tower_budget_rollups</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+        <x:v>Derived read model or reporting projection.</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
         <x:v>Medium</x:v>
@@ -664,16 +664,16 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>to_be_mapped</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
         <x:v>Tower</x:v>
       </x:c>
       <x:c r="C16" s="5" t="str">
-        <x:v>cio_tower.mart_value_funnel</x:v>
+        <x:v>public.tower_cloud_cost</x:v>
       </x:c>
       <x:c r="D16" s="5" t="str">
-        <x:v>Derived read model or reporting projection.</x:v>
+        <x:v>Persisted module object requiring owner review.</x:v>
       </x:c>
       <x:c r="E16" s="5" t="str">
         <x:v>Medium</x:v>
@@ -687,16 +687,16 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
         <x:v>Tower</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>cio_tower.measure_results</x:v>
+        <x:v>public.tower_dora_metrics</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
+        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
         <x:v>Medium</x:v>
@@ -710,13 +710,13 @@
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
         <x:v>Tower</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>cio_tower.measures</x:v>
+        <x:v>public.tower_program_financials</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
         <x:v>Persisted module object requiring owner review.</x:v>
@@ -733,16 +733,16 @@
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>to_be_mapped</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
         <x:v>Tower</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>public.ai_control_agent_outcomes</x:v>
+        <x:v>public.tower_spend_realism_audit</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+        <x:v>Persisted module object requiring owner review.</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
         <x:v>Medium</x:v>
@@ -756,16 +756,16 @@
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="5" t="str">
-        <x:v>Operational performance</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
         <x:v>Tower</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>public.ai_control_dora_metrics</x:v>
+        <x:v>public.tower_vendor_spend</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+        <x:v>Vendor, contract, or commercial-evidence substrate.</x:v>
       </x:c>
       <x:c r="E20" s="5" t="str">
         <x:v>Medium</x:v>
@@ -778,324 +778,25 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="B21" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C21" s="5" t="str">
-        <x:v>public.ai_control_spend_contracts</x:v>
-      </x:c>
-      <x:c r="D21" s="5" t="str">
-        <x:v>Risk/control governance or monitoring substrate.</x:v>
-      </x:c>
-      <x:c r="E21" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F21" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G21" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="B22" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C22" s="5" t="str">
-        <x:v>public.ai_tagged_budget_usd</x:v>
-      </x:c>
-      <x:c r="D22" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
-      </x:c>
-      <x:c r="E22" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F22" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G22" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="B23" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C23" s="5" t="str">
-        <x:v>public.budget</x:v>
-      </x:c>
-      <x:c r="D23" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
-      </x:c>
-      <x:c r="E23" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F23" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G23" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="B24" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C24" s="5" t="str">
-        <x:v>public.dora_baselines</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
-      </x:c>
-      <x:c r="E24" s="5" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="F24" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G24" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="B25" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C25" s="5" t="str">
-        <x:v>public.measurement</x:v>
-      </x:c>
-      <x:c r="D25" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
-      </x:c>
-      <x:c r="E25" s="5" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="F25" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G25" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="5" t="str">
-        <x:v>Generic metric</x:v>
-      </x:c>
-      <x:c r="B26" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C26" s="5" t="str">
-        <x:v>public.metrics</x:v>
-      </x:c>
-      <x:c r="D26" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
-      </x:c>
-      <x:c r="E26" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F26" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G26" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="B27" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C27" s="5" t="str">
-        <x:v>public.spend</x:v>
-      </x:c>
-      <x:c r="D27" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
-      </x:c>
-      <x:c r="E27" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F27" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G27" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="B28" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C28" s="5" t="str">
-        <x:v>public.tower_budget_rollups</x:v>
-      </x:c>
-      <x:c r="D28" s="5" t="str">
-        <x:v>Derived read model or reporting projection.</x:v>
-      </x:c>
-      <x:c r="E28" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F28" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G28" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="B29" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C29" s="5" t="str">
-        <x:v>public.tower_cloud_cost</x:v>
-      </x:c>
-      <x:c r="D29" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
-      </x:c>
-      <x:c r="E29" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F29" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G29" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="5" t="str">
-        <x:v>Operational performance</x:v>
-      </x:c>
-      <x:c r="B30" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C30" s="5" t="str">
-        <x:v>public.tower_dora_metrics</x:v>
-      </x:c>
-      <x:c r="D30" s="5" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
-      </x:c>
-      <x:c r="E30" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F30" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G30" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="5" t="str">
-        <x:v>knowledge.program</x:v>
-      </x:c>
-      <x:c r="B31" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C31" s="5" t="str">
-        <x:v>public.tower_program_financials</x:v>
-      </x:c>
-      <x:c r="D31" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
-      </x:c>
-      <x:c r="E31" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F31" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G31" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="B32" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C32" s="5" t="str">
-        <x:v>public.tower_spend_realism_audit</x:v>
-      </x:c>
-      <x:c r="D32" s="5" t="str">
-        <x:v>Persisted module object requiring owner review.</x:v>
-      </x:c>
-      <x:c r="E32" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F32" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G32" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="B33" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C33" s="5" t="str">
-        <x:v>public.tower_vendor_spend</x:v>
-      </x:c>
-      <x:c r="D33" s="5" t="str">
-        <x:v>Vendor, contract, or commercial-evidence substrate.</x:v>
-      </x:c>
-      <x:c r="E33" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F33" s="5" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G33" s="5" t="str">
-        <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="15" hidden="0" customHeight="1">
-      <x:c r="A34" s="6" t="str">
+      <x:c r="A21" s="6" t="str">
         <x:v>Value / outcome</x:v>
       </x:c>
-      <x:c r="B34" s="6" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="C34" s="6" t="str">
+      <x:c r="B21" s="6" t="str">
+        <x:v>Tower</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
         <x:v>public.value_states</x:v>
       </x:c>
-      <x:c r="D34" s="6" t="str">
-        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
-      </x:c>
-      <x:c r="E34" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="F34" s="6" t="str">
-        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
-      </x:c>
-      <x:c r="G34" s="6" t="str">
+      <x:c r="D21" s="6" t="str">
+        <x:v>Metric, KPI, value, or outcome measurement substrate.</x:v>
+      </x:c>
+      <x:c r="E21" s="6" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>shared metric definition registry; domain observations remain local until published</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str">
         <x:v>Separate metric definition from observation; reconcile units, period, tenant, and source lineage before consumption.</x:v>
       </x:c>
     </x:row>

--- a/reports/module-data-integration-audit/2026-07-27/METRIC_DEFINITION_DUPLICATION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/METRIC_DEFINITION_DUPLICATION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Duplication" sheetId="1" r:id="Rd36ae6c6f76a4f30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Duplication" sheetId="1" r:id="R40cc1de51b914b93"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/reports/module-data-integration-audit/2026-07-27/METRIC_DEFINITION_DUPLICATION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/METRIC_DEFINITION_DUPLICATION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Duplication" sheetId="1" r:id="R40cc1de51b914b93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Duplication" sheetId="1" r:id="R7e60af42340947d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -342,7 +342,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>Generic metric</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
         <x:v>Source</x:v>
@@ -365,7 +365,7 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
         <x:v>Source</x:v>
@@ -388,7 +388,7 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>knowledge.value_flow_step</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
         <x:v>Source</x:v>
@@ -411,7 +411,7 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>knowledge.value_driver_or_lever</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
         <x:v>Source</x:v>
@@ -434,7 +434,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
         <x:v>Source</x:v>
@@ -457,7 +457,7 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>knowledge.value_state_or_readiness</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
         <x:v>Source</x:v>
@@ -480,7 +480,7 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
         <x:v>Tower</x:v>
@@ -503,7 +503,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>knowledge.metric_observation</x:v>
+        <x:v>Generic metric</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
         <x:v>Tower</x:v>
@@ -549,7 +549,7 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>knowledge.outcome</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
         <x:v>Tower</x:v>
@@ -618,7 +618,7 @@
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
         <x:v>Tower</x:v>
@@ -641,7 +641,7 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
         <x:v>Tower</x:v>
@@ -664,7 +664,7 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
         <x:v>Tower</x:v>
@@ -687,7 +687,7 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>knowledge.metric_observation</x:v>
+        <x:v>Operational performance</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
         <x:v>Tower</x:v>
@@ -710,7 +710,7 @@
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>knowledge.metric_observation</x:v>
+        <x:v>Cost / spend / budget</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
         <x:v>Tower</x:v>
@@ -733,7 +733,7 @@
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
         <x:v>Tower</x:v>
@@ -756,7 +756,7 @@
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="5" t="str">
-        <x:v>knowledge.metric_observation</x:v>
+        <x:v>Cost / spend / budget</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
         <x:v>Tower</x:v>
@@ -779,7 +779,7 @@
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="6" t="str">
-        <x:v>Value / outcome</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="B21" s="6" t="str">
         <x:v>Tower</x:v>
